--- a/mistral_translate_work/split_by_prompt/excel/item/lang_item/lang_item__item__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/item/lang_item/lang_item__item__part_0002.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Vật phẩm dùng để thăng cấp Weapons.</t>
+          <t>Vật phẩm dùng để thăng cấp Vũ khí.</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
 Peeker: Con mắt.
 Wind-taker: Lỗ tai.
 Gold pole: Cái chân.
-The green: Weapons.
+The green: Vũ khí.
 The stick: Súng.
 ...</t>
         </is>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Weapons cướp được từ một kẻ Lưu Đày.</t>
+          <t>Vũ khí cướp được từ một kẻ Lưu Đày.</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Weapons từng bị băng đảng Madam Sow nhắm tới, giờ chủ nhân gốc dường như không còn quan trọng nữa.</t>
+          <t>Vũ khí từng bị băng đảng Madam Sow nhắm tới, giờ chủ nhân gốc dường như không còn quan trọng nữa.</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Weapons cướp được từ một kẻ Lưu Đày.</t>
+          <t>Vũ khí cướp được từ một kẻ Lưu Đày.</t>
         </is>
       </c>
     </row>
